--- a/artfynd/A 12084-2025 artfynd.xlsx
+++ b/artfynd/A 12084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123525933</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12084-2025 artfynd.xlsx
+++ b/artfynd/A 12084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123525933</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12084-2025 artfynd.xlsx
+++ b/artfynd/A 12084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123525933</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12084-2025 artfynd.xlsx
+++ b/artfynd/A 12084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123525933</v>
+        <v>123524970</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>96973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337480</v>
+        <v>337420</v>
       </c>
       <c r="R2" t="n">
-        <v>6434059</v>
+        <v>6434028</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +767,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Skogsklädd kulturmark blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,6 +788,241 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123525933</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>337480</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6434059</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123525117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96973</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>337412</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434023</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Skogsklädd kulturmark blandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12084-2025 artfynd.xlsx
+++ b/artfynd/A 12084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123524970</v>
+        <v>123525328</v>
       </c>
       <c r="B2" t="n">
-        <v>96973</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337420</v>
+        <v>337436</v>
       </c>
       <c r="R2" t="n">
-        <v>6434028</v>
+        <v>6433989</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,9 +762,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Skogsklädd kulturmark blandskog</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,16 +785,11 @@
         <v>123525933</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -914,15 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123525117</v>
+        <v>123526067</v>
       </c>
       <c r="B4" t="n">
-        <v>96973</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,27 +911,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337412</v>
+        <v>337571</v>
       </c>
       <c r="R4" t="n">
-        <v>6434023</v>
+        <v>6434062</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,13 +991,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Skogsklädd kulturmark blandskog</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,6 +1011,335 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123524970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337420</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434028</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Skogsklädd kulturmark blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123525117</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337412</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434023</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Skogsklädd kulturmark blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123312767</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skår 3:60, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>337419</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433995</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 plantor, även fler plantor i närområde. Vid basen av impediment/berg.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12084-2025 artfynd.xlsx
+++ b/artfynd/A 12084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525933</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526067</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525117</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,8 +1370,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123312767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>